--- a/Manufacturing Files/Nerdaxe_gamma_bom.xlsx
+++ b/Manufacturing Files/Nerdaxe_gamma_bom.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RogerPC\Desktop\bitaxeGamma-main\nerdaxe-gamma\Manufacturing Files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RogerPC\Desktop\bitaxeGamma-main\nerdaxe-gamma_v2.2\Manufacturing Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -15,14 +15,14 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Hoja1!$B$1:$D$48</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Hoja1!$B$1:$D$49</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="137">
   <si>
     <t>Observaciones</t>
   </si>
@@ -402,9 +402,6 @@
     <t>C8, C12, C29, C37, C38, C47, C49, C52, C53</t>
   </si>
   <si>
-    <t>C1, C5, C7, C26, C27, C28, C30, C31, C32, C33, C34, C35, C36, C39, C40, C41, C42, C44, C45, C46, C48</t>
-  </si>
-  <si>
     <t>R15, R17, R25</t>
   </si>
   <si>
@@ -424,6 +421,18 @@
   </si>
   <si>
     <t>C58464</t>
+  </si>
+  <si>
+    <t>C1, C5, C7, C26, C27, C28, C30, C31, C32, C33, C34, C35, C36, C39, C40, C41, C42, C44, C45, C46, C48, C23</t>
+  </si>
+  <si>
+    <t>R16, R20, R26, R27</t>
+  </si>
+  <si>
+    <t>Resistencia 0805 33 1% estandar</t>
+  </si>
+  <si>
+    <t>C17634</t>
   </si>
 </sst>
 </file>
@@ -970,7 +979,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D50"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1082,7 +1091,7 @@
         <v>33</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="C8" s="18" t="s">
         <v>70</v>
@@ -1348,7 +1357,7 @@
         <v>6</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C27" s="17" t="s">
         <v>56</v>
@@ -1386,107 +1395,115 @@
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" s="9" t="s">
-        <v>44</v>
+      <c r="A30" s="20">
+        <v>33</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C30" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="D30" s="25" t="s">
-        <v>128</v>
+        <v>134</v>
+      </c>
+      <c r="C30" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="D30" s="26" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C31" s="9" t="s">
-        <v>45</v>
+        <v>25</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>44</v>
       </c>
       <c r="D31" s="25" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" s="9" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="D32" s="25" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" s="9" t="s">
-        <v>91</v>
+        <v>7</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="C33" s="17" t="s">
-        <v>92</v>
+        <v>2</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>82</v>
       </c>
       <c r="D33" s="25" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" s="9" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C34" s="19" t="s">
-        <v>80</v>
+        <v>3</v>
+      </c>
+      <c r="C34" s="17" t="s">
+        <v>92</v>
       </c>
       <c r="D34" s="25" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C35" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="D35" s="25" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="B35" s="11" t="s">
+      <c r="B36" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="C35" s="9" t="s">
+      <c r="C36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="D35" s="25" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" s="4"/>
-      <c r="B36" s="12" t="s">
+      <c r="D36" s="25" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37" s="4"/>
+      <c r="B37" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C36" s="4"/>
-      <c r="D36" s="27"/>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" s="1"/>
-      <c r="B37" s="13"/>
-      <c r="C37" s="1"/>
-      <c r="D37" s="6"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="27"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" s="5"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="5"/>
+      <c r="A38" s="1"/>
+      <c r="B38" s="13"/>
+      <c r="C38" s="1"/>
       <c r="D38" s="6"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
@@ -1496,20 +1513,21 @@
       <c r="D39" s="6"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" s="2"/>
-      <c r="B40" s="15"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="8"/>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B43" s="10" t="s">
+      <c r="A40" s="5"/>
+      <c r="B40" s="14"/>
+      <c r="C40" s="5"/>
+      <c r="D40" s="6"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41" s="2"/>
+      <c r="B41" s="15"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="8"/>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B44" s="10" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" s="3"/>
-      <c r="B45" s="16"/>
-      <c r="D45" s="28"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" s="3"/>
@@ -1526,9 +1544,14 @@
       <c r="B48" s="16"/>
       <c r="D48" s="28"/>
     </row>
-    <row r="50" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C50" s="3"/>
-      <c r="D50" s="28"/>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49" s="3"/>
+      <c r="B49" s="16"/>
+      <c r="D49" s="28"/>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C51" s="3"/>
+      <c r="D51" s="28"/>
     </row>
   </sheetData>
   <pageMargins left="0.56000000000000005" right="0.34" top="0.48" bottom="0.75" header="0.3" footer="0.3"/>
